--- a/output/2025_A24_SECCION_E.xlsx
+++ b/output/2025_A24_SECCION_E.xlsx
@@ -826,7 +826,7 @@
     <t>Servicio de Salud Metropolitano Oriente</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>Servicio de Salud Metropolitano Central</t>
